--- a/facit/kahoot-statistik-2026-09-11.xlsx
+++ b/facit/kahoot-statistik-2026-09-11.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:H28"/>
+  <dimension ref="A2:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -469,7 +469,14 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Importér i Kahoot: create.kahoot.it → Opret → Importér regneark. Ret ikke i rækkefølgen af kolonner.</t>
+          <t>Importér i Kahoot: create.kahoot.it → Opret → Importér regneark. Byt ikke om på kolonnerne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Billederne kan ikke følge med i en import. Træk dem ind bagefter — filnavnet starter med spørgsmålets nummer.</t>
         </is>
       </c>
     </row>
@@ -697,27 +704,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Hvilke fem tal tegnes et boksplot ud fra?</t>
+          <t>Talrækken er 3, 5, 5, 6, 8, 9, 13. Hvad er den øvre kvartil?</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Mindste, nedre kvartil, median, øvre kvartil, største</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Mindste, gennemsnit, median, typetal, største</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>De fem mindste tal i datasættet</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Gennemsnit, median, typetal, sum og antal</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
@@ -733,27 +740,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Hvad sker der med medianen, hvis det største tal bliver dobbelt så stort?</t>
+          <t>Hvilke fem tal tegnes et boksplot ud fra?</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Ingenting</t>
+          <t>Mindste, nedre kvartil, median, øvre kvartil, største</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Den bliver dobbelt så stor</t>
+          <t>Mindste, gennemsnit, median, typetal, største</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Den stiger lidt</t>
+          <t>De fem mindste tal i datasættet</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Den falder</t>
+          <t>Gennemsnit, median, typetal, sum og antal</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
@@ -769,27 +776,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>40 unger. 15 spiller håndbold. Hvor mange grader fylder håndbold i et cirkeldiagram?</t>
+          <t>Hvor stor en del af observationerne ligger inde i boksplottets kasse?</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>135°</t>
+          <t>50 %</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>150°</t>
+          <t>25 %</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>90°</t>
+          <t>75 %</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>100 %</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
@@ -805,27 +812,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>40 unger. 8 svømmer. Hvor mange grader fylder svømning i et cirkeldiagram?</t>
+          <t>Aflæs medianen på boksplottet.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>72°</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>80°</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>45°</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
@@ -841,27 +848,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>40 unger. 10 spiller fodbold. Hvor mange procent er det?</t>
+          <t>Hvad sker der med medianen, hvis det største tal bliver dobbelt så stort?</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>25 %</t>
+          <t>Ingenting</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>10 %</t>
+          <t>Den bliver dobbelt så stor</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>40 %</t>
+          <t>Den stiger lidt</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>15 %</t>
+          <t>Den falder</t>
         </is>
       </c>
       <c r="G18" s="4" t="n">
@@ -877,31 +884,31 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Hvad skal alle frekvenserne i en tabel tilsammen give?</t>
+          <t>Talrækken er 4, 6, 8, 10, 12. Hvad er gennemsnittet?</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>100 %</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>360 %</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Antallet af observationer</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Gennemsnittet</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>1</v>
@@ -913,27 +920,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Hvor på en sumkurve aflæser man medianen?</t>
+          <t>40 unger. 15 spiller håndbold. Hvor mange grader fylder håndbold i cirklen?</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Ved 50 % på den lodrette akse</t>
+          <t>135°</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Ved 50 % på den vandrette akse</t>
+          <t>150°</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Ved kurvens højeste punkt</t>
+          <t>90°</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Midt mellem første og sidste punkt</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -949,27 +956,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Frekvenserne er 20 %, 35 % og 25 %. Hvad er den kumulerede frekvens efter tredje interval?</t>
+          <t>40 unger. 8 svømmer. Hvor mange grader fylder svømning i cirklen?</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>80 %</t>
+          <t>72°</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>25 %</t>
+          <t>80°</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>100 %</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>35 %</t>
+          <t>45°</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -985,27 +992,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Du kaster to terninger. Hvad er sandsynligheden for at summen bliver 7?</t>
+          <t>40 unger. 10 spiller fodbold. Hvor mange procent er det?</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>6 ud af 36</t>
+          <t>25 %</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1 ud af 36</t>
+          <t>10 %</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>7 ud af 36</t>
+          <t>40 %</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>1 ud af 12</t>
+          <t>15 %</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
@@ -1021,31 +1028,31 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Du kaster to terninger. Hvad er sandsynligheden for mindst én sekser?</t>
+          <t>Hvilken sektor er størst i cirkeldiagrammet?</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>11 ud af 36</t>
+          <t>Håndbold</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6 ud af 36</t>
+          <t>Fodbold</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>12 ud af 36</t>
+          <t>Svømning</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>2 ud af 36</t>
+          <t>Andet</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>1</v>
@@ -1057,31 +1064,31 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Tilslutningen steg fra 15 % til 21 %. Hvor mange PROCENTPOINT er det steget?</t>
+          <t>Hvad skal alle frekvenserne i en tabel tilsammen give?</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6 procentpoint</t>
+          <t>100 %</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>40 procentpoint</t>
+          <t>360 %</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>6 procent</t>
+          <t>Antallet af observationer</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>21 procentpoint</t>
+          <t>Gennemsnittet</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>1</v>
@@ -1093,27 +1100,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Tilslutningen steg fra 15 % til 21 %. Hvor mange PROCENT er det steget?</t>
+          <t>Hvor på en sumkurve aflæser man medianen?</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>40 %</t>
+          <t>Ved 50 % på den lodrette akse</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6 %</t>
+          <t>Ved 50 % på den vandrette akse</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>21 %</t>
+          <t>Ved kurvens højeste punkt</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>36 %</t>
+          <t>Midt mellem første og sidste punkt</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
@@ -1129,27 +1136,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Et spørgeskema sendes til 400 unger. 38 svarer. Hvad er svarprocenten?</t>
+          <t>Aflæs medianen på sumkurven. Hvad er den cirka?</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>9,5 %</t>
+          <t>Omkring 172 cm</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>38 %</t>
+          <t>Omkring 160 cm</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>10,5 %</t>
+          <t>Omkring 180 cm</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>90,5 %</t>
+          <t>Omkring 155 cm</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -1165,27 +1172,27 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Et diagram har en y-akse, der starter ved 199 i stedet for 0. Hvad sker der?</t>
+          <t>Frekvenserne er 20 %, 35 % og 25 %. Hvad er den kumulerede frekvens efter tredje interval?</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Forskellene ser større ud, end de er</t>
+          <t>80 %</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Forskellene ser mindre ud, end de er</t>
+          <t>25 %</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Ingenting — tallene er jo de samme</t>
+          <t>100 %</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Diagrammet bliver ulovligt</t>
+          <t>35 %</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
@@ -1201,33 +1208,393 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Fem lønninger: fire omkring 24.000 kr og én på 400.000 kr. Hvad beskriver bedst en typisk løn?</t>
+          <t>Hvilket interval har flest unger i histogrammet?</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>4-6 timer</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>0-2 timer</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2-4 timer</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>6-8 timer</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Hvad er typetallet ifølge søjlediagrammet?</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2 gange</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>1 gang</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>3 gange</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>4 gange</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Du kaster to terninger. Hvad er sandsynligheden for at summen bliver 7?</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>6 ud af 36</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>1 ud af 36</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>7 ud af 36</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1 ud af 12</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Hvor mange af de 36 udfald giver summen 5?</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Du kaster to terninger. Hvad er sandsynligheden for mindst én sekser?</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>11 ud af 36</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>6 ud af 36</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>12 ud af 36</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>2 ud af 36</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Tilslutningen steg fra 15 % til 21 %. Hvor mange PROCENTPOINT er det steget?</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>6 procentpoint</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>40 procentpoint</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>6 procent</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>21 procentpoint</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Tilslutningen steg fra 15 % til 21 %. Hvor mange PROCENT er det steget?</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>40 %</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>6 %</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>21 %</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>36 %</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Et spørgeskema sendes til 400 unger. 38 svarer. Hvad er svarprocenten?</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>9,5 %</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>38 %</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>10,5 %</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>90,5 %</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Et diagrams y-akse starter ved 199 i stedet for 0. Hvad sker der?</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Forskellene ser større ud, end de er</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Forskellene ser mindre ud, end de er</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Ingenting — tallene er jo de samme</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Diagrammet bliver ulovligt</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>En figurs side fordobles. Hvor mange gange større bliver arealet?</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>4 gange</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>2 gange</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>8 gange</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>16 gange</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Fire lønninger omkring 24.000 kr og én på 400.000 kr. Hvad er en typisk løn?</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
           <t>Medianen, 24.000 kr</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Gennemsnittet, 98.800 kr</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Den højeste løn</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Summen af de fem</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H28" s="4" t="n">
+      <c r="G38" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" s="4" t="n">
         <v>1</v>
       </c>
     </row>

--- a/facit/kahoot-statistik-2026-09-11.xlsx
+++ b/facit/kahoot-statistik-2026-09-11.xlsx
@@ -529,29 +529,29 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="G9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -565,29 +565,29 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -606,12 +606,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -637,29 +637,29 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="G12" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -673,29 +673,29 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="G13" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -709,29 +709,29 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="G14" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -745,29 +745,29 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>Gennemsnit, median, typetal, sum og antal</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>Mindste, nedre kvartil, median, øvre kvartil, største</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Mindste, gennemsnit, median, typetal, største</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>De fem mindste tal i datasættet</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Gennemsnit, median, typetal, sum og antal</t>
-        </is>
-      </c>
       <c r="G15" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -781,14 +781,14 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>25 %</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>50 %</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>25 %</t>
-        </is>
-      </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
           <t>75 %</t>
@@ -803,7 +803,7 @@
         <v>30</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -817,19 +817,19 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>7</t>
@@ -839,7 +839,7 @@
         <v>30</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -853,29 +853,29 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>Den stiger lidt</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Den falder</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Den bliver dobbelt så stor</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
           <t>Ingenting</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>Den bliver dobbelt så stor</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Den stiger lidt</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Den falder</t>
-        </is>
-      </c>
       <c r="G18" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -889,29 +889,29 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="G19" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -925,29 +925,29 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>90°</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>15°</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
           <t>135°</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>150°</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>90°</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>15°</t>
-        </is>
-      </c>
       <c r="G20" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -961,29 +961,29 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>80°</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>45°</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>8°</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
           <t>72°</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>80°</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>8°</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>45°</t>
-        </is>
-      </c>
       <c r="G21" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -997,19 +997,19 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
+          <t>40 %</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
           <t>25 %</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>10 %</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>40 %</t>
-        </is>
-      </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>15 %</t>
@@ -1019,7 +1019,7 @@
         <v>30</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1033,29 +1033,29 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
+          <t>Svømning</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Andet</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
           <t>Håndbold</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Fodbold</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Svømning</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Andet</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1069,29 +1069,29 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
+          <t>360 %</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Gennemsnittet</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
           <t>100 %</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>360 %</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Antallet af observationer</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Gennemsnittet</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1141,29 +1141,29 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
+          <t>Omkring 155 cm</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Omkring 160 cm</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
           <t>Omkring 172 cm</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Omkring 160 cm</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Omkring 180 cm</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Omkring 155 cm</t>
-        </is>
-      </c>
       <c r="G26" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1177,29 +1177,29 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
+          <t>25 %</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
           <t>80 %</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>25 %</t>
-        </is>
-      </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
+          <t>35 %</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
           <t>100 %</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>35 %</t>
-        </is>
-      </c>
       <c r="G27" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1213,17 +1213,17 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
+          <t>2-4 timer</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>0-2 timer</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
           <t>4-6 timer</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>0-2 timer</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>2-4 timer</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1249,29 +1249,29 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
+          <t>4 gange</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
           <t>2 gange</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>3 gange</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1 gang</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>3 gange</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>4 gange</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1285,19 +1285,19 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
+          <t>7 ud af 36</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>1 ud af 36</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
           <t>6 ud af 36</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>1 ud af 36</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>7 ud af 36</t>
-        </is>
-      </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>1 ud af 12</t>
@@ -1307,7 +1307,7 @@
         <v>30</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
+          <t>2 ud af 36</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
           <t>12 ud af 36</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2 ud af 36</t>
         </is>
       </c>
       <c r="G32" s="4" t="n">
@@ -1393,29 +1393,29 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
+          <t>21 procentpoint</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
           <t>6 procentpoint</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>6 procent</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>40 procentpoint</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>6 procent</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>21 procentpoint</t>
-        </is>
-      </c>
       <c r="G33" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1434,17 +1434,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
+          <t>36 %</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>21 %</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
           <t>6 %</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>21 %</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>36 %</t>
         </is>
       </c>
       <c r="G34" s="4" t="n">
@@ -1465,29 +1465,29 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
+          <t>38 %</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
           <t>9,5 %</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>38 %</t>
-        </is>
-      </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
+          <t>90,5 %</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
           <t>10,5 %</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>90,5 %</t>
-        </is>
-      </c>
       <c r="G35" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
+          <t>Ingenting — tallene er jo de samme</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Diagrammet bliver ulovligt</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
           <t>Forskellene ser mindre ud, end de er</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Ingenting — tallene er jo de samme</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Diagrammet bliver ulovligt</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
@@ -1537,29 +1537,29 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
+          <t>8 gange</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>2 gange</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>16 gange</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
           <t>4 gange</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>2 gange</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>8 gange</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>16 gange</t>
-        </is>
-      </c>
       <c r="G37" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1573,29 +1573,29 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
+          <t>Gennemsnittet, 98.800 kr</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Summen af de fem</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Den højeste løn</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
           <t>Medianen, 24.000 kr</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>Gennemsnittet, 98.800 kr</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Den højeste løn</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Summen af de fem</t>
-        </is>
-      </c>
       <c r="G38" s="4" t="n">
         <v>30</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
